--- a/Dataset/Parameters Configuration.xlsx
+++ b/Dataset/Parameters Configuration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unigeit-my.sharepoint.com/personal/christian_gianoglio_unige_it/Documents/Università/Cosmic/Cosmic GitHub/Force_recontruction_algorithm/Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="11_F25DC773A252ABDACC1048E6419842F25BDE58F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C4D449B-9B07-43AC-BA60-977F621BC973}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="11_F25DC773A252ABDACC1048E6419842F25BDE58F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F3E48CD-586D-4FF7-84E7-939DAD377FCD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
   <si>
     <t>NW</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>28 no release</t>
   </si>
   <si>
     <t>13,17,18</t>
@@ -150,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -163,6 +160,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" customWidth="1"/>
@@ -504,7 +502,7 @@
       <c r="D2" s="3">
         <v>10</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <v>1</v>
       </c>
       <c r="F2" s="3">
@@ -537,7 +535,7 @@
       <c r="D3" s="3">
         <v>10</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="3">
         <v>1</v>
       </c>
       <c r="F3" s="3">
@@ -570,7 +568,7 @@
       <c r="D4" s="3">
         <v>10</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="3">
         <v>1</v>
       </c>
       <c r="F4" s="3">
@@ -588,9 +586,7 @@
       <c r="J4" s="1">
         <v>10</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -605,7 +601,7 @@
       <c r="D5" s="3">
         <v>10</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>1</v>
       </c>
       <c r="F5" s="3">
@@ -638,7 +634,7 @@
       <c r="D6" s="3">
         <v>10</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>1</v>
       </c>
       <c r="F6" s="3">
@@ -671,7 +667,7 @@
       <c r="D7" s="3">
         <v>10</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <v>1</v>
       </c>
       <c r="F7" s="3">
@@ -689,9 +685,7 @@
       <c r="J7" s="1">
         <v>10</v>
       </c>
-      <c r="K7" s="6">
-        <v>26</v>
-      </c>
+      <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -706,7 +700,7 @@
       <c r="D8" s="3">
         <v>10</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="3">
         <v>1</v>
       </c>
       <c r="F8" s="3">
@@ -724,9 +718,10 @@
       <c r="J8" s="3">
         <v>10</v>
       </c>
-      <c r="K8" s="6">
-        <v>26</v>
-      </c>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E9" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -798,7 +793,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3">
         <v>0.3</v>
@@ -831,7 +826,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="2">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
         <v>0.3</v>
@@ -864,7 +859,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="2">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3">
         <v>0.3</v>
@@ -897,7 +892,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="2">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3">
         <v>0.3</v>
@@ -914,9 +909,7 @@
       <c r="J5" s="1">
         <v>10</v>
       </c>
-      <c r="K5" s="6">
-        <v>17</v>
-      </c>
+      <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -932,7 +925,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="2">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3">
         <v>0.3</v>
@@ -965,7 +958,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="2">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3">
         <v>0.3</v>
@@ -982,9 +975,7 @@
       <c r="J7" s="1">
         <v>10</v>
       </c>
-      <c r="K7" s="6">
-        <v>5</v>
-      </c>
+      <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1000,7 +991,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="2">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3">
         <v>0.3</v>
@@ -1096,7 +1087,7 @@
         <v>10</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
